--- a/ОБЖ/lab1/Определение скорости движения воздуха шаровым кататермометром.xlsx
+++ b/ОБЖ/lab1/Определение скорости движения воздуха шаровым кататермометром.xlsx
@@ -16,313 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>м/c</t>
-  </si>
-  <si>
-    <t>1,38</t>
-  </si>
-  <si>
-    <t>0,048</t>
-  </si>
-  <si>
-    <t>1,42</t>
-  </si>
-  <si>
-    <t>0,062</t>
-  </si>
-  <si>
-    <t>1,47</t>
-  </si>
-  <si>
-    <t>0,077</t>
-  </si>
-  <si>
-    <t>1,51</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>2,1</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>2,81</t>
-  </si>
-  <si>
-    <t>1,27</t>
-  </si>
-  <si>
-    <t>2,14</t>
-  </si>
-  <si>
-    <t>0,48</t>
-  </si>
-  <si>
-    <t>2,85</t>
-  </si>
-  <si>
-    <t>1,31</t>
-  </si>
-  <si>
-    <t>2,16</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>2,89</t>
-  </si>
-  <si>
-    <t>1,35</t>
-  </si>
-  <si>
-    <t>2,22</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>2,93</t>
-  </si>
-  <si>
-    <t>1,39</t>
-  </si>
-  <si>
-    <t>1,55</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>2,26</t>
-  </si>
-  <si>
-    <t>0,62</t>
-  </si>
-  <si>
-    <t>2,97</t>
-  </si>
-  <si>
-    <t>1,43</t>
-  </si>
-  <si>
-    <t>1,59</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>3,02</t>
-  </si>
-  <si>
-    <t>1,48</t>
-  </si>
-  <si>
-    <t>1,63</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>2,35</t>
-  </si>
-  <si>
-    <t>0,73</t>
-  </si>
-  <si>
-    <t>3,06</t>
-  </si>
-  <si>
-    <t>1,52</t>
-  </si>
-  <si>
-    <t>1,68</t>
-  </si>
-  <si>
-    <t>0,16</t>
-  </si>
-  <si>
-    <t>2,39</t>
-  </si>
-  <si>
-    <t>0,80</t>
-  </si>
-  <si>
-    <t>3,1</t>
-  </si>
-  <si>
-    <t>1,57</t>
-  </si>
-  <si>
-    <t>1,72</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>2,43</t>
-  </si>
-  <si>
-    <t>0,88</t>
-  </si>
-  <si>
-    <t>3,14</t>
-  </si>
-  <si>
-    <t>1,60</t>
-  </si>
-  <si>
-    <t>1,76</t>
-  </si>
-  <si>
-    <t>0,20</t>
-  </si>
-  <si>
-    <t>2,47</t>
-  </si>
-  <si>
-    <t>0,97</t>
-  </si>
-  <si>
-    <t>3,18</t>
-  </si>
-  <si>
-    <t>1,65</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>2,51</t>
-  </si>
-  <si>
-    <t>1,00</t>
-  </si>
-  <si>
-    <t>3,23</t>
-  </si>
-  <si>
-    <t>1,70</t>
-  </si>
-  <si>
-    <t>1,84</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>2,55</t>
-  </si>
-  <si>
-    <t>1,03</t>
-  </si>
-  <si>
-    <t>3,27</t>
-  </si>
-  <si>
-    <t>1,75</t>
-  </si>
-  <si>
-    <t>1,89</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>2,6</t>
-  </si>
-  <si>
-    <t>1,07</t>
-  </si>
-  <si>
-    <t>3,31</t>
-  </si>
-  <si>
-    <t>1,79</t>
-  </si>
-  <si>
-    <t>1,93</t>
-  </si>
-  <si>
-    <t>0,30</t>
-  </si>
-  <si>
-    <t>2,64</t>
-  </si>
-  <si>
-    <t>1,11</t>
-  </si>
-  <si>
-    <t>3,35</t>
-  </si>
-  <si>
-    <t>1,97</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>2,68</t>
-  </si>
-  <si>
-    <t>1,15</t>
-  </si>
-  <si>
-    <t>3,39</t>
-  </si>
-  <si>
-    <t>2,01</t>
-  </si>
-  <si>
-    <t>0,36</t>
-  </si>
-  <si>
-    <t>2,72</t>
-  </si>
-  <si>
-    <t>1,19</t>
-  </si>
-  <si>
-    <t>3,43</t>
-  </si>
-  <si>
-    <t>1,94</t>
-  </si>
-  <si>
-    <t>2,05</t>
-  </si>
-  <si>
-    <t>0,40</t>
-  </si>
-  <si>
-    <t>2,77</t>
-  </si>
-  <si>
-    <t>1,22</t>
-  </si>
-  <si>
-    <t>3,48</t>
-  </si>
-  <si>
-    <t>1,98</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <r>
       <t>С</t>
@@ -336,44 +30,22 @@
         <family val="2"/>
         <charset val="204"/>
       </rPr>
-      <t>к</t>
+      <t>к мДж/cм2·с·град</t>
     </r>
   </si>
   <si>
-    <r>
-      <t>мДж/cм</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t>·с·град</t>
-    </r>
+    <t>V м/c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0000000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0000000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,14 +62,6 @@
     </font>
     <font>
       <vertAlign val="subscript"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -436,11 +100,11 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -736,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
@@ -744,12 +408,12 @@
     <col min="3" max="3" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -760,28 +424,28 @@
       <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="A2" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="B2" s="4">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4"/>
+      <c r="A3" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6.2E-2</v>
+      </c>
+      <c r="C3" s="5"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -790,13 +454,13 @@
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2"/>
+      <c r="A4" s="3">
+        <v>1.47</v>
+      </c>
+      <c r="B4" s="3">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="C4" s="5"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -805,13 +469,13 @@
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2"/>
+      <c r="A5" s="3">
+        <v>1.51</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="C5" s="5"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -820,13 +484,13 @@
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2"/>
+      <c r="A6" s="3">
+        <v>1.55</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="C6" s="5"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -835,13 +499,13 @@
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="2"/>
+      <c r="A7" s="3">
+        <v>1.59</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="C7" s="5"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -850,13 +514,13 @@
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="2"/>
+      <c r="A8" s="3">
+        <v>1.63</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C8" s="5"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -865,13 +529,13 @@
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2"/>
+      <c r="A9" s="3">
+        <v>1.68</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="C9" s="5"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -880,13 +544,13 @@
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="2"/>
+      <c r="A10" s="3">
+        <v>1.72</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="C10" s="5"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -895,13 +559,13 @@
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="2"/>
+      <c r="A11" s="3">
+        <v>1.76</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -910,13 +574,13 @@
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="2"/>
+      <c r="A12" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="C12" s="5"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -925,13 +589,13 @@
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="2"/>
+      <c r="A13" s="3">
+        <v>1.84</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="C13" s="5"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -940,13 +604,13 @@
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="2"/>
+      <c r="A14" s="3">
+        <v>1.89</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="C14" s="5"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -955,13 +619,13 @@
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="2"/>
+      <c r="A15" s="3">
+        <v>1.93</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="C15" s="5"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -970,13 +634,13 @@
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="2"/>
+      <c r="A16" s="3">
+        <v>1.97</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="C16" s="5"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -985,13 +649,13 @@
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="2"/>
+      <c r="A17" s="3">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="C17" s="5"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -1000,13 +664,13 @@
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="2"/>
+      <c r="A18" s="3">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="C18" s="5"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1015,13 +679,13 @@
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="2"/>
+      <c r="A19" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.44</v>
+      </c>
+      <c r="C19" s="5"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -1030,13 +694,13 @@
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="2"/>
+      <c r="A20" s="3">
+        <v>2.14</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="C20" s="5"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -1045,13 +709,13 @@
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2"/>
+      <c r="A21" s="3">
+        <v>2.16</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="C21" s="5"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1060,13 +724,13 @@
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="2"/>
+      <c r="A22" s="3">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="C22" s="5"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1075,13 +739,13 @@
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="2"/>
+      <c r="A23" s="3">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="C23" s="5"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -1090,13 +754,13 @@
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="2"/>
+      <c r="A24" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="C24" s="5"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -1105,13 +769,13 @@
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="2"/>
+      <c r="A25" s="3">
+        <v>2.35</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.73</v>
+      </c>
+      <c r="C25" s="5"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -1120,13 +784,13 @@
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="2"/>
+      <c r="A26" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="C26" s="5"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -1135,13 +799,13 @@
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="2"/>
+      <c r="A27" s="3">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="B27" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="C27" s="5"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -1150,13 +814,13 @@
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="2"/>
+      <c r="A28" s="3">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="B28" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="C28" s="5"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1165,13 +829,13 @@
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="2"/>
+      <c r="A29" s="3">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -1180,13 +844,13 @@
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="2"/>
+      <c r="A30" s="3">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1.03</v>
+      </c>
+      <c r="C30" s="5"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -1195,13 +859,13 @@
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="2"/>
+      <c r="A31" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1.07</v>
+      </c>
+      <c r="C31" s="5"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -1210,13 +874,13 @@
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="2"/>
+      <c r="A32" s="3">
+        <v>2.64</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C32" s="5"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -1225,13 +889,13 @@
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="2"/>
+      <c r="A33" s="3">
+        <v>2.68</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C33" s="5"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -1240,13 +904,13 @@
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="2"/>
+      <c r="A34" s="3">
+        <v>2.72</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="C34" s="5"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -1255,13 +919,13 @@
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C35" s="2"/>
+      <c r="A35" s="3">
+        <v>2.77</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1.22</v>
+      </c>
+      <c r="C35" s="5"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -1270,13 +934,13 @@
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" s="2"/>
+      <c r="A36" s="3">
+        <v>2.81</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="C36" s="5"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -1285,13 +949,13 @@
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="2"/>
+      <c r="A37" s="3">
+        <v>2.85</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="C37" s="5"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -1300,13 +964,13 @@
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="2"/>
+      <c r="A38" s="3">
+        <v>2.89</v>
+      </c>
+      <c r="B38" s="3">
+        <v>1.35</v>
+      </c>
+      <c r="C38" s="5"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -1315,13 +979,13 @@
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="2"/>
+      <c r="A39" s="3">
+        <v>2.93</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1.39</v>
+      </c>
+      <c r="C39" s="5"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -1330,13 +994,13 @@
       <c r="I39" s="2"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="2"/>
+      <c r="A40" s="3">
+        <v>2.97</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1.43</v>
+      </c>
+      <c r="C40" s="5"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -1345,13 +1009,13 @@
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="2"/>
+      <c r="A41" s="3">
+        <v>3.02</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="C41" s="5"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
@@ -1360,13 +1024,13 @@
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="2"/>
+      <c r="A42" s="3">
+        <v>3.06</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1.52</v>
+      </c>
+      <c r="C42" s="5"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -1375,13 +1039,13 @@
       <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="2"/>
+      <c r="A43" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1.57</v>
+      </c>
+      <c r="C43" s="5"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -1390,13 +1054,13 @@
       <c r="I43" s="2"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" s="2"/>
+      <c r="A44" s="3">
+        <v>3.14</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="C44" s="5"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -1405,13 +1069,13 @@
       <c r="I44" s="2"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="2"/>
+      <c r="A45" s="3">
+        <v>3.18</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="C45" s="5"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -1420,13 +1084,13 @@
       <c r="I45" s="2"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="2"/>
+      <c r="A46" s="3">
+        <v>3.23</v>
+      </c>
+      <c r="B46" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="C46" s="5"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -1435,13 +1099,13 @@
       <c r="I46" s="2"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="2"/>
+      <c r="A47" s="3">
+        <v>3.27</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="C47" s="5"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -1450,13 +1114,13 @@
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="2"/>
+      <c r="A48" s="3">
+        <v>3.31</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1.79</v>
+      </c>
+      <c r="C48" s="5"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
@@ -1465,13 +1129,13 @@
       <c r="I48" s="2"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" s="2"/>
+      <c r="A49" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1.84</v>
+      </c>
+      <c r="C49" s="5"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -1480,13 +1144,13 @@
       <c r="I49" s="2"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="2"/>
+      <c r="A50" s="3">
+        <v>3.39</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1.89</v>
+      </c>
+      <c r="C50" s="5"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -1495,13 +1159,13 @@
       <c r="I50" s="2"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="2"/>
+      <c r="A51" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1.94</v>
+      </c>
+      <c r="C51" s="5"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -1510,13 +1174,13 @@
       <c r="I51" s="2"/>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C52" s="2"/>
+      <c r="A52" s="3">
+        <v>3.48</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1.98</v>
+      </c>
+      <c r="C52" s="5"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -1525,12 +1189,8 @@
       <c r="I52" s="2"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -1582,17 +1242,6 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
